--- a/Store_Personnel_Safety_Walk_Template.xlsx
+++ b/Store_Personnel_Safety_Walk_Template.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Are the "Wet Floor" cones/signs visible in all areas during rain and mopping?</t>
+          <t>Are the "Wet Floor" cones/signs visible in all areas during rain and mopping? (Please ensure we dry mop often during these times and remove "Wet Floor" cones/signs when area is dry)</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>The doors are NOT being propped open for a vendor delivery?</t>
+          <t>Are backroom doors closed or held open with a door stop? (Do not prop open with water or other merchandise)</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
